--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>Authorization.typeId.nullFlavor</t>
@@ -1491,7 +1487,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1499,10 +1495,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1600,39 +1596,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1683,7 +1679,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1703,39 +1699,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1786,7 +1782,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1806,39 +1802,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1847,49 +1843,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1909,17 +1905,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1937,11 +1933,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1992,7 +1988,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2012,10 +2008,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2042,7 +2038,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2093,7 +2089,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2113,10 +2109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2150,7 +2146,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2172,7 +2168,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2190,7 +2186,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2210,10 +2206,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2236,10 +2232,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2291,7 +2287,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2311,10 +2307,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2412,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2513,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2606,7 +2602,7 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>74</v>
@@ -2614,10 +2610,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2715,39 +2711,39 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2798,7 +2794,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2818,39 +2814,39 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2901,7 +2897,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2921,39 +2917,39 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2962,49 +2958,49 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3024,17 +3020,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3052,11 +3048,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3107,7 +3103,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3127,10 +3123,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3157,7 +3153,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3208,7 +3204,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3228,10 +3224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3265,7 +3261,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3287,25 +3283,25 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3325,10 +3321,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3362,7 +3358,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>74</v>
@@ -3384,25 +3380,25 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3422,10 +3418,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3451,7 +3447,7 @@
         <v>95</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3503,7 +3499,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3523,10 +3519,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3549,10 +3545,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3580,29 +3576,29 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3622,10 +3618,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3681,25 +3677,25 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3719,10 +3715,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3820,10 +3816,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3851,13 +3847,13 @@
         <v>85</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3865,49 +3861,49 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3927,17 +3923,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -3955,11 +3951,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4010,7 +4006,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4030,17 +4026,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4058,11 +4054,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4113,7 +4109,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4133,17 +4129,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4161,11 +4157,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4216,7 +4212,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4236,17 +4232,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4264,11 +4260,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4319,7 +4315,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4339,10 +4335,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4365,11 +4361,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4420,7 +4416,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4440,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4466,11 +4462,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4521,7 +4517,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4541,39 +4537,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4624,7 +4620,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4644,39 +4640,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4727,7 +4723,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4747,39 +4743,39 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4830,7 +4826,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>authorization</t>
+    <t>CDA - authorization</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -936,42 +936,42 @@
   <dimension ref="A1:AK38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.5703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.21484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.21484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.6953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.44140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.60546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="24.3828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2123,7 +2123,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/main/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
